--- a/backtest_runs/20260410_193731/by_symbol/DFML/DFML.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/DFML/DFML.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -679,7 +679,7 @@
         <v>-9399</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>95613.8</v>
@@ -817,7 +817,7 @@
         <v>-1942.460000000003</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="3" t="n">
         <v>95676.46000000001</v>
@@ -863,7 +863,7 @@
         <v>-1942.460000000003</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="3" t="n">
         <v>93734</v>
@@ -909,7 +909,7 @@
         <v>-2443.739999999993</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>91290.26000000001</v>
@@ -1182,10 +1182,10 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>93671.34</v>
@@ -1228,10 +1228,10 @@
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K17" s="2" t="n">
         <v>93671.34</v>
@@ -1274,10 +1274,10 @@
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>93671.34</v>
@@ -1415,7 +1415,7 @@
         <v>-1942.460000000003</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>91728.88</v>
@@ -1461,7 +1461,7 @@
         <v>-751.9199999999951</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="3" t="n">
         <v>90976.96000000001</v>
